--- a/appointment_forms/032_new_patient_covid_19_test_registration_form--appointment_forms.xlsx
+++ b/appointment_forms/032_new_patient_covid_19_test_registration_form--appointment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Other (Specify)</t>
+          <t>Medical Insurance Other</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Other (Specify)</t>
+          <t>Medical Condition Other</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other (Specify)</t>
+          <t>Medical History Other</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other (Specify)</t>
+          <t>Test Location Other</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other (Specify)</t>
+          <t>Doctor Name Other</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1118,12 +1118,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship</t>
+          <t>emergency_contact_relationship_2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Relationship</t>
+          <t>Emergency Contact Relationship 2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Other (Specify)</t>
+          <t>Emergency Contact Relationship Other</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1262,7 +1262,7 @@
   <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1542,7 +1542,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship_choices</t>
+          <t>emergency_contact_relationship_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1559,7 +1559,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship_choices</t>
+          <t>emergency_contact_relationship_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship_choices</t>
+          <t>emergency_contact_relationship_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1593,7 +1593,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship_choices</t>
+          <t>emergency_contact_relationship_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
